--- a/survey_templates/045_personal_finance_strategy_survey--survey_templates.xlsx
+++ b/survey_templates/045_personal_finance_strategy_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>financial_institution</t>
+          <t>financial_institution_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Financial Institution</t>
+          <t>Financial Institution 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Financial Institution</t>
+          <t>Financial Institutions</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>financial_institute</t>
+          <t>financial_institute_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Financial Institute</t>
+          <t>Financial Institute 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>financial_planning_method</t>
+          <t>financial_planning_method_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Financial Planning Method</t>
+          <t>Financial Planning Method 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>financial_institutions</t>
+          <t>financial_institutions_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financial Institutions</t>
+          <t>Financial Institutions 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>financial_institution</t>
+          <t>financial_institution_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Financial Institution</t>
+          <t>Financial Institution 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>financial_institutions</t>
+          <t>financial_institutions_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Financial Institutions</t>
+          <t>Financial Institutions 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>financial_strategy</t>
+          <t>financial_strategy_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Financial Strategy</t>
+          <t>Financial Strategy 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>financial_institute_choices</t>
+          <t>financial_institute_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>financial_institute_choices</t>
+          <t>financial_institute_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>financial_institute_choices</t>
+          <t>financial_institute_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>financial_institute_choices</t>
+          <t>financial_institute_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>financial_institute_choices</t>
+          <t>financial_institute_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>financial_planning_method_choices</t>
+          <t>financial_planning_method_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>financial_planning_method_choices</t>
+          <t>financial_planning_method_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>financial_planning_method_choices</t>
+          <t>financial_planning_method_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>financial_planning_method_choices</t>
+          <t>financial_planning_method_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>financial_planning_method_choices</t>
+          <t>financial_planning_method_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>financial_planning_method_choices</t>
+          <t>financial_planning_method_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_3_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_3_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_3_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_3_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>financial_institution_choices</t>
+          <t>financial_institution_3_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_3_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2129,7 +2129,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_3_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_3_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_3_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>financial_institutions_choices</t>
+          <t>financial_institutions_3_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
